--- a/dcf/WGS.xlsx
+++ b/dcf/WGS.xlsx
@@ -472,7 +472,7 @@
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>Opus: 13.0x</t>
+        <t>User-edited — overridden from Opus 13.0x</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
@@ -1168,184 +1168,184 @@
     </row>
     <row r="5">
       <c r="A5" s="53" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>72.13411499634078</v>
+        <v>74.73839762507438</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>69.58228542011094</v>
+        <v>72.07267134748523</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>67.14380500441912</v>
+        <v>69.52574961626173</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>64.81301510370679</v>
+        <v>67.0916899708881</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>62.58456655897383</v>
+        <v>64.76487536398078</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>60.45340139649937</v>
+        <v>62.53999490167406</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>58.41473568679077</v>
+        <v>60.41202580575258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="53" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>76.47458604423012</v>
+        <v>79.07886867296371</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>73.73292863240142</v>
+        <v>76.22331455977572</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>71.11371269082348</v>
+        <v>73.49565730266607</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>68.61080654900897</v>
+        <v>70.88948141619025</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>66.21841456731875</v>
+        <v>68.39872337232566</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>63.93105723845721</v>
+        <v>66.0176507436319</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>61.74355255172713</v>
+        <v>63.74084267068895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="53" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>80.81505709211943</v>
+        <v>83.41933972085305</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>77.88357184469191</v>
+        <v>80.37395777206621</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>75.08362037722783</v>
+        <v>77.46556498907043</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>72.40859799431112</v>
+        <v>74.68727286149242</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>69.85226257566363</v>
+        <v>72.03257138067056</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>67.40871308041503</v>
+        <v>69.49530658558973</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>65.07236941666349</v>
+        <v>67.06965953562532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="53" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>85.15552814000877</v>
+        <v>87.75981076874235</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>82.0342150569824</v>
+        <v>84.52460098435671</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>79.05352806363219</v>
+        <v>81.4354726754748</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>76.20638943961329</v>
+        <v>78.48506430679458</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>73.48611058400853</v>
+        <v>75.66641938901546</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>70.88636892237287</v>
+        <v>72.97296242754757</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>68.40118628159986</v>
+        <v>70.39847640056168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="53" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>89.49599918789811</v>
+        <v>92.10028181663169</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>86.18485826927289</v>
+        <v>88.67524419664718</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>83.02343575003653</v>
+        <v>85.40538036187915</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>80.00418088491547</v>
+        <v>82.28285575209675</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>77.11995859235341</v>
+        <v>79.30026739736036</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>74.36402476433071</v>
+        <v>76.45061826950541</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>71.73000314653623</v>
+        <v>73.72729326549806</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="53" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>93.83647023578743</v>
+        <v>96.44075286452103</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>90.33550148156338</v>
+        <v>92.82588740893767</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>86.99334343644088</v>
+        <v>89.37528804828349</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>83.80197233021762</v>
+        <v>86.08064719739892</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>80.75380660069833</v>
+        <v>82.93411540570527</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>77.84168060628853</v>
+        <v>79.92827411146325</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>75.05882001147259</v>
+        <v>77.05611013043442</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="53" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>98.17694128367675</v>
+        <v>100.7812239124104</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>94.48614469385389</v>
+        <v>96.97653062122818</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>90.96325112284525</v>
+        <v>93.34519573468785</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>87.59976377551979</v>
+        <v>89.8784386427011</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>84.38765460904321</v>
+        <v>86.56796341405015</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>81.31933644824637</v>
+        <v>83.40592995342108</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>78.38763687640896</v>
+        <v>80.38492699537078</v>
       </c>
     </row>
     <row r="13">
@@ -1368,7 +1368,7 @@
         <v>0.130580706199631</v>
       </c>
       <c r="C14" s="57" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
     </row>
   </sheetData>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.956867702769053</v>
+        <v>0.9516798366042153</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24479,7 +24479,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="46">
@@ -24676,13 +24676,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>76.20638943961329</v>
+        <v>78.48506430679458</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>104.5156855786111</v>
+        <v>107.3797387858674</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>54.34617636763649</v>
+        <v>56.13635591730088</v>
       </c>
     </row>
     <row r="59">
@@ -25494,9 +25494,9 @@
         <f>Dashboard!B45</f>
         <v/>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Opus</t>
+      <c r="D40" s="32" t="inlineStr">
+        <is>
+          <t>user-edited</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -25504,7 +25504,11 @@
           <t>13.0x</t>
         </is>
       </c>
-      <c r="F40" s="31" t="inlineStr"/>
+      <c r="F40" s="31" t="inlineStr">
+        <is>
+          <t>overridden from Opus 13.0x</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">

--- a/dcf/WGS.xlsx
+++ b/dcf/WGS.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
